--- a/viethoa/sakumoyu-0054-kuro_002.xlsx
+++ b/viethoa/sakumoyu-0054-kuro_002.xlsx
@@ -4491,11 +4491,15 @@
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Quay về ngủ thôi.</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>帰って眠ろう。</t>
+          <t>Quay về ngủ thôi.</t>
         </is>
       </c>
     </row>
@@ -4512,11 +4516,15 @@
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Cùng nhau, bây giờ cả hai sẽ ngủ cho đến sáng.</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[・|ふ][・|た][・|り]で一緒に、今は朝まで眠るんだ。</t>
+          <t>Cùng nhau, bây giờ cả hai sẽ ngủ cho đến sáng.</t>
         </is>
       </c>
     </row>
@@ -4533,11 +4541,15 @@
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Nhen nhóm hi vọng về ngày được gặp lại cô bé trong "giấc mơ" một lần nữa.</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>また“夢”の中で[・|あ][・|の][・|子]と逢える日に“希望”を抱いて。</t>
+          <t>Nhen nhóm hi vọng về ngày được gặp lại cô bé trong "giấc mơ" một lần nữa.</t>
         </is>
       </c>
     </row>
@@ -4554,11 +4566,15 @@
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Khẽ ngân nga một "khúc hát" quen thuộc, tôi quay trở về.</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>歌い慣れた小さな“歌”を口ずさみ、俺は戻った。</t>
+          <t>Khẽ ngân nga một "khúc hát" quen thuộc, tôi quay trở về.</t>
         </is>
       </c>
     </row>
@@ -4579,11 +4595,15 @@
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>...K-Khoan đã, chờ chút.</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>……ちょっと、待ってくれ</t>
+          <t>...K-Khoan đã, chờ chút.</t>
         </is>
       </c>
     </row>
@@ -4600,11 +4620,15 @@
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Nghe đến đó, tôi cắt ngang lời cô gái— Đó quả là một trải nghiệm kì lạ.</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>そこまで聞いて、俺は女の子の話を遮断した――不思議な体験ではあった。</t>
+          <t>Nghe đến đó, tôi cắt ngang lời cô gái— Đó quả là một trải nghiệm kì lạ.</t>
         </is>
       </c>
     </row>
@@ -4621,11 +4645,15 @@
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Ngay khi cô gái bắt đầu kể, tôi nhắm mắt lại. Để rồi cảm giác như đang mơ, những hình ảnh và âm thanh trong câu chuyện ấy cứ thế được tái hiện lại trong tâm trí tôi.</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>女の子が話し始め、[まぶた|瞼]を閉じる。するとまるで夢を見るみたいにして、心の中に、語り聞かされる映像が、音が、再生されるような感覚に包まれていた。</t>
+          <t>Ngay khi cô gái bắt đầu kể, tôi nhắm mắt lại. Để rồi cảm giác như đang mơ, những hình ảnh và âm thanh trong câu chuyện ấy cứ thế được tái hiện lại trong tâm trí tôi.</t>
         </is>
       </c>
     </row>
@@ -4642,11 +4670,15 @@
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Nhưng điều kì lạ nhất có lẽ là cảm giác "chuyện đương nhiên phải thế" (hoặc giả là tôi bị áp đặt suy nghĩ như vậy).</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>もっとも不思議であったのは、“そういうものだ”と思えてしまう（あるいは思わされてしまっているのか）感覚のほうであるかもしれない。</t>
+          <t>Nhưng điều kì lạ nhất có lẽ là cảm giác "chuyện đương nhiên phải thế" (hoặc giả là tôi bị áp đặt suy nghĩ như vậy).</t>
         </is>
       </c>
     </row>
@@ -4663,11 +4695,15 @@
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Nhưng lúc này, trước khi bận tâm về những điều đó, tôi còn có chuyện khác đáng lưu tâm hơn.</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>だが今は、それらに声を上げるよりもまず、気になることがあった。</t>
+          <t>Nhưng lúc này, trước khi bận tâm về những điều đó, tôi còn có chuyện khác đáng lưu tâm hơn.</t>
         </is>
       </c>
     </row>
@@ -4688,11 +4724,15 @@
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>...Tại sao thế?</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>……どうして？</t>
+          <t>...Tại sao thế?</t>
         </is>
       </c>
     </row>
@@ -4709,11 +4749,15 @@
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Giọng nói của cô gái vang lên từ đầu dây bên kia.</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>電話の向こうから聞こえる女の子の声だ。</t>
+          <t>Giọng nói của cô gái vang lên từ đầu dây bên kia.</t>
         </is>
       </c>
     </row>
@@ -4734,11 +4778,15 @@
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>...Tại sao lại bảo tớ "chờ một chút"?</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>……どうして、ちょっと待って、なの？</t>
+          <t>...Tại sao lại bảo tớ "chờ một chút"?</t>
         </is>
       </c>
     </row>
@@ -4755,11 +4803,15 @@
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Giọng nói ấy dường như đang run lên vì bất an.</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>その声は不安に震えているようでもあった。</t>
+          <t>Giọng nói ấy dường như đang run lên vì bất an.</t>
         </is>
       </c>
     </row>
@@ -4780,11 +4832,15 @@
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Hãy nói cho tớ biết.</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>教えてほしい</t>
+          <t>Hãy nói cho tớ biết.</t>
         </is>
       </c>
     </row>
@@ -4805,11 +4861,15 @@
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>...Nói chuyện gì cơ?</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>……なにを</t>
+          <t>...Nói chuyện gì cơ?</t>
         </is>
       </c>
     </row>
@@ -4830,11 +4890,15 @@
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Câu chuyện đó là về tớ đúng không?</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>それって俺の話、なんだよな</t>
+          <t>Câu chuyện đó là về tớ đúng không?</t>
         </is>
       </c>
     </row>
@@ -4855,11 +4919,15 @@
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>...Ừm.</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>……うん</t>
+          <t>...Ừm.</t>
         </is>
       </c>
     </row>
@@ -4880,11 +4948,15 @@
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Tương lai của cậu. Hoặc là quá khứ.</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>あなたの未来。あるいは過去</t>
+          <t>Tương lai của cậu. Hoặc là quá khứ.</t>
         </is>
       </c>
     </row>
@@ -4901,11 +4973,15 @@
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Nghe giọng nói thì thầm khe khẽ ấy, tôi chỉ muốn ôm đầu vì bối rối.</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>囁くように響くその声に、だけど俺は頭を抱えたい。そんな気分だ。</t>
+          <t>Nghe giọng nói thì thầm khe khẽ ấy, tôi chỉ muốn ôm đầu vì bối rối.</t>
         </is>
       </c>
     </row>
@@ -4926,11 +5002,15 @@
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Quá khứ của tớ. Hoặc là tương lai sao...?</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>俺の、過去の話。あるいは、未来の話……？</t>
+          <t>Quá khứ của tớ. Hoặc là tương lai sao...?</t>
         </is>
       </c>
     </row>
@@ -4947,11 +5027,15 @@
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Dù tự lẩm nhẩm nhưng nỗi hoài nghi trong tôi vẫn không hề vơi đi.</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>つぶやいてみても疑念は晴れない。</t>
+          <t>Dù tự lẩm nhẩm nhưng nỗi hoài nghi trong tôi vẫn không hề vơi đi.</t>
         </is>
       </c>
     </row>
@@ -4968,11 +5052,15 @@
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>...Tôi hoàn toàn không có chút kí ức nào về nó cả.</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>……まったく覚えがないのだ。</t>
+          <t>...Tôi hoàn toàn không có chút kí ức nào về nó cả.</t>
         </is>
       </c>
     </row>
@@ -4989,11 +5077,15 @@
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Những lời cô gái kể nghe cứ như là câu chuyện của ai đó xa lạ chứ chẳng phải của tôi.</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>語り聞かされるものはまるで他人事のようにしか響いてこない。</t>
+          <t>Những lời cô gái kể nghe cứ như là câu chuyện của ai đó xa lạ chứ chẳng phải của tôi.</t>
         </is>
       </c>
     </row>
@@ -5014,11 +5106,15 @@
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Câu chuyện tương lai, tức là những sự việc vẫn chưa xảy ra với tớ bây giờ đúng không. Nếu thế, việc tớ chẳng nhớ gì cũng là điều hiển nhiên thôi...</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>未来の話ってことは、つまり、まだ今の俺には起きてない出来事だってことなのかな。そうなると、今の俺に、身に覚えなんてなくても当然ってことに……</t>
+          <t>Câu chuyện tương lai, tức là những sự việc vẫn chưa xảy ra với tớ bây giờ đúng không. Nếu thế, việc tớ chẳng nhớ gì cũng là điều hiển nhiên thôi...</t>
         </is>
       </c>
     </row>
@@ -5035,11 +5131,15 @@
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Không.</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>いや。</t>
+          <t>Không.</t>
         </is>
       </c>
     </row>
@@ -5056,11 +5156,15 @@
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Câu chuyện về tương lai sao.</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>未来の話って。</t>
+          <t>Câu chuyện về tương lai sao.</t>
         </is>
       </c>
     </row>
@@ -5077,11 +5181,15 @@
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Liệu mình có nên tin vào những điều đó không.</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>そんなことを信じるのか。</t>
+          <t>Liệu mình có nên tin vào những điều đó không.</t>
         </is>
       </c>
     </row>
@@ -5098,11 +5206,15 @@
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Rốt cuộc cô bé này là ai? Cô ấy đang muốn truyền đạt điều gì cho tôi cơ chứ?</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>そもそもこの子は誰なのか。いったい何を俺に伝えようとしているのか。</t>
+          <t>Rốt cuộc cô bé này là ai? Cô ấy đang muốn truyền đạt điều gì cho tôi cơ chứ?</t>
         </is>
       </c>
     </row>
@@ -5119,11 +5231,15 @@
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Nỗi hoài nghi trong tôi không dứt, và sự hoang mang cũng vậy.</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>疑念は尽きない。困惑もだ。</t>
+          <t>Nỗi hoài nghi trong tôi không dứt, và sự hoang mang cũng vậy.</t>
         </is>
       </c>
     </row>
@@ -5144,11 +5260,15 @@
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Hơn nữa tớ cũng đâu có năng lực kì lạ kiểu như nhìn thấy "cái chết" hay gì đó đâu...</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>それに俺には、“死”が見えるとか、そんなおかしな力なんてまったくないし……</t>
+          <t>Hơn nữa tớ cũng đâu có năng lực kì lạ kiểu như nhìn thấy "cái chết" hay gì đó đâu...</t>
         </is>
       </c>
     </row>
@@ -5169,11 +5289,15 @@
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Chuyện đó...</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>それは</t>
+          <t>Chuyện đó...</t>
         </is>
       </c>
     </row>
@@ -5194,11 +5318,15 @@
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Ừm.</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>ああ</t>
+          <t>Ừm.</t>
         </is>
       </c>
     </row>
@@ -5219,11 +5347,15 @@
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>...Bởi vì đó là "năng lực" sẽ biến mất khi cậu trưởng thành.</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>……それは、ね。大人になれば消えてしまう“能力”だから</t>
+          <t>...Bởi vì đó là "năng lực" sẽ biến mất khi cậu trưởng thành.</t>
         </is>
       </c>
     </row>
@@ -5240,11 +5372,15 @@
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>"Vì con người ai cũng trở nên đặc biệt khi còn nhỏ mà." Cô gái khẽ cất giọng yếu ớt.</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>人間はみんな、子どもの頃は特別だから。女の子は微かな声で言った。</t>
+          <t>"Vì con người ai cũng trở nên đặc biệt khi còn nhỏ mà." Cô gái khẽ cất giọng yếu ớt.</t>
         </is>
       </c>
     </row>
@@ -5265,11 +5401,15 @@
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Tất cả những gì liên quan đến "Dạ", bao gồm cả việc từng sở hữu năng lực đó, đều sẽ bị xóa sạch khỏi kí ức của cậu.</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>そういう力があったってことを含めて、記憶の中からも消えてしまう――“夜”に関することはすべて、そうなる</t>
+          <t>Tất cả những gì liên quan đến "Dạ", bao gồm cả việc từng sở hữu năng lực đó, đều sẽ bị xóa sạch khỏi kí ức của cậu.</t>
         </is>
       </c>
     </row>
@@ -5290,11 +5430,15 @@
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>...“Dạ” sao?</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>……“夜”？</t>
+          <t>...“Dạ” sao?</t>
         </is>
       </c>
     </row>
@@ -5315,11 +5459,15 @@
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -5336,11 +5484,15 @@
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Leng keng...</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>チリン、と。</t>
+          <t>Leng keng...</t>
         </is>
       </c>
     </row>
@@ -5357,11 +5509,15 @@
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Có tiếng chuông nhỏ vang lên từ đầu dây bên kia.</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>電話の向こうから小さな鈴の音が聞こえた。</t>
+          <t>Có tiếng chuông nhỏ vang lên từ đầu dây bên kia.</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5538,15 @@
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>...Tớ kể tiếp nhé?</t>
+        </is>
+      </c>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>……続き。話しても、いい？</t>
+          <t>...Tớ kể tiếp nhé?</t>
         </is>
       </c>
     </row>
@@ -5407,11 +5567,15 @@
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>À, ừ.</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>あ、ああ</t>
+          <t>À, ừ.</t>
         </is>
       </c>
     </row>
@@ -5428,11 +5592,15 @@
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Dù đáp lại như vậy, nhưng trong lòng tôi không khỏi tự vấn liệu mình có thực sự nên nghe tiếp hay không.</t>
+        </is>
+      </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>そう答えながらも、この先を聞いてしまって本当にいいのだろうか。そんな思いがないわけではない。</t>
+          <t>Dù đáp lại như vậy, nhưng trong lòng tôi không khỏi tự vấn liệu mình có thực sự nên nghe tiếp hay không.</t>
         </is>
       </c>
     </row>
@@ -5453,11 +5621,15 @@
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Cậu từng nói rằng câu chuyện này có thể sẽ làm tổn thương tớ, nhưng...</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>君は、もしかしたら俺のことを傷つけてしまうかもしれないって、そう言ってたけれど……</t>
+          <t>Cậu từng nói rằng câu chuyện này có thể sẽ làm tổn thương tớ, nhưng...</t>
         </is>
       </c>
     </row>
@@ -5474,11 +5646,15 @@
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Sự ngập ngừng này thực chất chính là nỗi sợ hãi.</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>この躊躇いの正体は、きっと恐怖だ。</t>
+          <t>Sự ngập ngừng này thực chất chính là nỗi sợ hãi.</t>
         </is>
       </c>
     </row>
@@ -5495,11 +5671,15 @@
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Nếu nghe thêm nữa, liệu tôi có bước vào con đường không thể quay đầu lại được chăng?</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>これ以上、話を聞いてしまえば、俺はもう後戻りできなくなってしまうのではないか。</t>
+          <t>Nếu nghe thêm nữa, liệu tôi có bước vào con đường không thể quay đầu lại được chăng?</t>
         </is>
       </c>
     </row>
@@ -5516,11 +5696,15 @@
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Ngay cả việc bước một bước ra khỏi cuộc sống tẻ nhạt ngập tràn mỏi mệt thường nhật cũng khiến tôi cảm thấy sợ hãi.</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>平凡な苦しみを繰り返す毎日からでさえ、一歩踏み出すことが怖いと感じる。</t>
+          <t>Ngay cả việc bước một bước ra khỏi cuộc sống tẻ nhạt ngập tràn mỏi mệt thường nhật cũng khiến tôi cảm thấy sợ hãi.</t>
         </is>
       </c>
     </row>
@@ -5537,11 +5721,15 @@
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Thế nhưng, đồng thời tôi cũng mong muốn được thay đổi biết bao. Lòng tôi dấy lên niềm kì vọng lớn lao.</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>だけど、同じくらい、[・|変][・|わ][・|り][・|た][・|い]。そんな期待が胸の中にある。</t>
+          <t>Thế nhưng, đồng thời tôi cũng mong muốn được thay đổi biết bao. Lòng tôi dấy lên niềm kì vọng lớn lao.</t>
         </is>
       </c>
     </row>
@@ -5558,11 +5746,15 @@
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Mọi chuyện đáng lẽ ra không nên như thế này.</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>こんなはずじゃなかった。</t>
+          <t>Mọi chuyện đáng lẽ ra không nên như thế này.</t>
         </is>
       </c>
     </row>
@@ -5579,11 +5771,15 @@
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Có phải đáng lẽ tôi đã có một cuộc đời khác, một cuộc đời tươi đẹp hơn chăng...</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>俺にはもっと違う、別の人生があったのではないか……。</t>
+          <t>Có phải đáng lẽ tôi đã có một cuộc đời khác, một cuộc đời tươi đẹp hơn chăng...</t>
         </is>
       </c>
     </row>
@@ -5600,11 +5796,15 @@
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Bởi vì ý nghĩ ấy cứ mãi đeo bám tôi.</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>そんな思いが消えずにあるから。</t>
+          <t>Bởi vì ý nghĩ ấy cứ mãi đeo bám tôi.</t>
         </is>
       </c>
     </row>
@@ -5621,11 +5821,15 @@
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Bởi vì thực tại chỉ toàn những điều tồi tệ khiến tôi mệt mỏi khôn cùng.</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>嫌なことばかりの[・|今]が苦しくて、仕方がないから。</t>
+          <t>Bởi vì thực tại chỉ toàn những điều tồi tệ khiến tôi mệt mỏi khôn cùng.</t>
         </is>
       </c>
     </row>
@@ -5642,11 +5846,15 @@
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Nên dù cho có phải đối diện với một quá khứ và tương lai tàn nhẫn đến thế nào đi chăng nữa...</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>たとえどんなに残酷な過去を、そして未来を、突きつけられるのだとしても……。</t>
+          <t>Nên dù cho có phải đối diện với một quá khứ và tương lai tàn nhẫn đến thế nào đi chăng nữa...</t>
         </is>
       </c>
     </row>
@@ -5663,11 +5871,15 @@
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Nếu ở đây, tôi có thể tìm lại được điều gì đó dường như đã lãng quên trong thời thơ ấu xa xôi, thì hiện thực tầm thường này của tôi biết đâu sẽ có sự chuyển biến.</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>ここで、遠い子ども時代に忘れてきてしまっているらしい何かを取り戻せたなら、俺の平凡な現実は何か変わるかもしれない。</t>
+          <t>Nếu ở đây, tôi có thể tìm lại được điều gì đó dường như đã lãng quên trong thời thơ ấu xa xôi, thì hiện thực tầm thường này của tôi biết đâu sẽ có sự chuyển biến.</t>
         </is>
       </c>
     </row>
@@ -5684,11 +5896,15 @@
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Gửi gắm niềm hi vọng ích kỉ ấy vào lời nói— tôi cất tiếng: "Hãy kể cho tớ nghe đi."</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
-          <t>そんな都合の良い希望を込めて、言う――聞かせてほしい。</t>
+          <t>Gửi gắm niềm hi vọng ích kỉ ấy vào lời nói— tôi cất tiếng: "Hãy kể cho tớ nghe đi."</t>
         </is>
       </c>
     </row>
@@ -5709,11 +5925,15 @@
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>...Kể tiếp cho tớ nghe câu chuyện đó đi.</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
-          <t>……話の続き、聞かせてほしいよ</t>
+          <t>...Kể tiếp cho tớ nghe câu chuyện đó đi.</t>
         </is>
       </c>
     </row>
@@ -5734,11 +5954,15 @@
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -5755,11 +5979,15 @@
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Tiếng chuông lại vang lên leng keng.</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>チリンとまた鈴の音がした。</t>
+          <t>Tiếng chuông lại vang lên leng keng.</t>
         </is>
       </c>
     </row>
@@ -5776,11 +6004,15 @@
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Đó chính là câu trả lời.</t>
+        </is>
+      </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
-          <t>それが答えだ。</t>
+          <t>Đó chính là câu trả lời.</t>
         </is>
       </c>
     </row>
@@ -5797,11 +6029,15 @@
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Quá khứ của tôi. Hoặc tương lai.</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>俺の過去。あるいは、未来。</t>
+          <t>Quá khứ của tôi. Hoặc tương lai.</t>
         </is>
       </c>
     </row>
@@ -5818,11 +6054,15 @@
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Khoảng thời gian mơ hồ ấy lại một lần nữa bắt đầu.</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>そんなあやふやな時間が再びはじまる。</t>
+          <t>Khoảng thời gian mơ hồ ấy lại một lần nữa bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -5843,11 +6083,15 @@
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>...Trước hết, hãy bắt đầu từ câu chuyện về giấc mơ của cậu.</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>……まずは、あなたの夢の話から</t>
+          <t>...Trước hết, hãy bắt đầu từ câu chuyện về giấc mơ của cậu.</t>
         </is>
       </c>
     </row>
@@ -5864,11 +6108,15 @@
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Cô gái bắt đầu tiếp tục kể bằng chất giọng có phần ngập ngừng, chậm rãi.</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>女の子は少しずつ、たどたどしくもある口調で、続きを語り始めてくれる。</t>
+          <t>Cô gái bắt đầu tiếp tục kể bằng chất giọng có phần ngập ngừng, chậm rãi.</t>
         </is>
       </c>
     </row>
@@ -5889,11 +6137,15 @@
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>...Cậu, người sở hữu một chút năng lực đặc biệt, đã gặp gỡ một "giấc mơ" tỏa sáng trắng tinh khôi giữa "Dạ" đặc biệt.</t>
+        </is>
+      </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>……少し特別な力を持ったあなたは、特別な“夜”の中で、まっしろに輝く“夢”と出会った</t>
+          <t>...Cậu, người sở hữu một chút năng lực đặc biệt, đã gặp gỡ một "giấc mơ" tỏa sáng trắng tinh khôi giữa "Dạ" đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -5914,11 +6166,15 @@
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Đôi tay vươn về phía nhau...</t>
+        </is>
+      </c>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>手と手を伸ばし</t>
+          <t>Đôi tay vươn về phía nhau...</t>
         </is>
       </c>
     </row>
@@ -5939,11 +6195,15 @@
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>...Trao nhau nụ cười mỉm.</t>
+        </is>
+      </c>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>……微笑み合って</t>
+          <t>...Trao nhau nụ cười mỉm.</t>
         </is>
       </c>
     </row>
@@ -5964,11 +6224,15 @@
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Thế nhưng, hai người lại ở trong "Dạ", nơi không bao giờ có thể chạm vào nhau...</t>
+        </is>
+      </c>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>でも、ふたりはけして、触れられもしない“夜”の中……</t>
+          <t>Thế nhưng, hai người lại ở trong "Dạ", nơi không bao giờ có thể chạm vào nhau...</t>
         </is>
       </c>
     </row>
@@ -5989,11 +6253,15 @@
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>...Các cậu đã phải lòng nhau.</t>
+        </is>
+      </c>
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
-          <t>……[・|あ][・|な][・|た][・|達]は、恋をする</t>
+          <t>...Các cậu đã phải lòng nhau.</t>
         </is>
       </c>
     </row>
@@ -6014,11 +6282,15 @@
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>...Hả?</t>
+        </is>
+      </c>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>……え？</t>
+          <t>...Hả?</t>
         </is>
       </c>
     </row>
@@ -6039,11 +6311,15 @@
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Và rồi cậu sẽ biết được... người anh hùng thực sự đã đi đâu.</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>そうしてあなたは知ってしまうの。本当のヒーローは、どこに行ってしまったのかを</t>
+          <t>Và rồi cậu sẽ biết được... người anh hùng thực sự đã đi đâu.</t>
         </is>
       </c>
     </row>
@@ -6064,11 +6340,15 @@
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -6085,11 +6365,15 @@
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Liệu bản thân đã thực sự sẵn sàng để nhận lấy tổn thương chưa?</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>傷つくための覚悟は本当にできているのか。</t>
+          <t>Liệu bản thân đã thực sự sẵn sàng để nhận lấy tổn thương chưa?</t>
         </is>
       </c>
     </row>
@@ -6106,11 +6390,15 @@
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Tôi cảm giác như câu chuyện đang đưa ra lời chất vấn đó.</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>そう問いかけられているようにも感じた。</t>
+          <t>Tôi cảm giác như câu chuyện đang đưa ra lời chất vấn đó.</t>
         </is>
       </c>
     </row>
@@ -6127,11 +6415,15 @@
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Vì vậy, tôi không nói thêm lời nào nữa, chỉ lặng lẽ lắng nghe giọng nói của cô gái.</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>だから俺はもう何も言わず、ただただ静かに、女の子の声に耳を傾けた。</t>
+          <t>Vì vậy, tôi không nói thêm lời nào nữa, chỉ lặng lẽ lắng nghe giọng nói của cô gái.</t>
         </is>
       </c>
     </row>
@@ -6148,11 +6440,15 @@
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Tôi nghe thấy một "khúc ca".</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>“歌”が聞こえる。</t>
+          <t>Tôi nghe thấy một "khúc ca".</t>
         </is>
       </c>
     </row>
@@ -6169,11 +6465,15 @@
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Đó là một "khúc ca" với giai điệu êm đềm nhưng đầy mạnh mẽ, tựa như những cánh hoa rơi lả tả giữa màn đêm.</t>
+        </is>
+      </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>はらはらと夜に舞う花びらみらいに、静かで、しかしとても力強くもある旋律を持つ“歌”だった。</t>
+          <t>Đó là một "khúc ca" với giai điệu êm đềm nhưng đầy mạnh mẽ, tựa như những cánh hoa rơi lả tả giữa màn đêm.</t>
         </is>
       </c>
     </row>
@@ -6190,11 +6490,15 @@
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Tôi có cảm giác như mình đang được vẫy gọi bởi khúc ca khó quên ấy...</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
-          <t>忘れがたいその“歌”に、まるで呼ばれているような気がして……、</t>
+          <t>Tôi có cảm giác như mình đang được vẫy gọi bởi khúc ca khó quên ấy...</t>
         </is>
       </c>
     </row>
@@ -6215,11 +6519,15 @@
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -6236,11 +6544,15 @@
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Tôi tỉnh giấc.</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>目覚める。</t>
+          <t>Tôi tỉnh giấc.</t>
         </is>
       </c>
     </row>
@@ -6257,11 +6569,15 @@
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Tôi mở mắt.</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>[まぶた|瞼]を開く。</t>
+          <t>Tôi mở mắt.</t>
         </is>
       </c>
     </row>
@@ -6278,11 +6594,15 @@
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Và rồi, tôi nhận ra mình đang đứng ở một nơi vô cùng lộng lẫy.</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>すると、自分がきらびやかな場所に立っていることに、気づいた。</t>
+          <t>Và rồi, tôi nhận ra mình đang đứng ở một nơi vô cùng lộng lẫy.</t>
         </is>
       </c>
     </row>
@@ -6303,11 +6623,15 @@
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Nơi này là...</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>ここは……</t>
+          <t>Nơi này là...</t>
         </is>
       </c>
     </row>
@@ -6324,11 +6648,15 @@
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Cứ như thể tôi đang lạc bước vào trong một bức tranh vậy.</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>まるで絵画の中に迷い込んでしまったようだ。</t>
+          <t>Cứ như thể tôi đang lạc bước vào trong một bức tranh vậy.</t>
         </is>
       </c>
     </row>
@@ -6345,11 +6673,15 @@
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Đó là ấn tượng đầu tiên của tôi về nơi này.</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>まずそれが最初に抱いた感想だった。</t>
+          <t>Đó là ấn tượng đầu tiên của tôi về nơi này.</t>
         </is>
       </c>
     </row>
@@ -6366,11 +6698,15 @@
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Một thành phố về đêm lấp lánh rực rỡ.</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>きらきら眩しい夜の街。</t>
+          <t>Một thành phố về đêm lấp lánh rực rỡ.</t>
         </is>
       </c>
     </row>
@@ -6387,11 +6723,15 @@
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Những sinh vật kì lạ đang qua lại khắp nơi.</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>そこらを行き交う不思議なもの達。</t>
+          <t>Những sinh vật kì lạ đang qua lại khắp nơi.</t>
         </is>
       </c>
     </row>
@@ -6408,11 +6748,15 @@
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Ngay cả bầu trời khi ngước nhìn lên cũng thật kì bí.</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>見上げた空さえ不可思議だった。</t>
+          <t>Ngay cả bầu trời khi ngước nhìn lên cũng thật kì bí.</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6773,15 @@
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Trên bầu trời rực rỡ sắc màu của hoa kia, không có lấy một chòm sao quen thuộc nào.</t>
+        </is>
+      </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>花の色彩に彩られた空には、見知った星座はひとつもなかった。</t>
+          <t>Trên bầu trời rực rỡ sắc màu của hoa kia, không có lấy một chòm sao quen thuộc nào.</t>
         </is>
       </c>
     </row>
@@ -6450,11 +6798,15 @@
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Những hạt sáng trắng muốt, dịu nhẹ cứ lững lờ bay lên dù trời không một gợn gió.</t>
+        </is>
+      </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>柔らかいまっしろな光りの粒が、風もないのにふわりふわりと、舞い上がっていく。</t>
+          <t>Những hạt sáng trắng muốt, dịu nhẹ cứ lững lờ bay lên dù trời không một gợn gió.</t>
         </is>
       </c>
     </row>
@@ -6475,11 +6827,15 @@
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>...Để xem nào.</t>
+        </is>
+      </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>……ええっと</t>
+          <t>...Để xem nào.</t>
         </is>
       </c>
     </row>
@@ -6496,11 +6852,15 @@
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Tôi vừa ngẩn ngơ dõi theo hướng bay của các hạt sáng, vừa suy nghĩ.</t>
+        </is>
+      </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>光りの粒子の行き先を、ぼんやりと視線で追いながら、思う。</t>
+          <t>Tôi vừa ngẩn ngơ dõi theo hướng bay của các hạt sáng, vừa suy nghĩ.</t>
         </is>
       </c>
     </row>
@@ -6517,11 +6877,15 @@
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Đáng lẽ ra mình đã đi ngủ như thường lệ rồi chứ.</t>
+        </is>
+      </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>俺は、いつものように眠りについたはず。</t>
+          <t>Đáng lẽ ra mình đã đi ngủ như thường lệ rồi chứ.</t>
         </is>
       </c>
     </row>
@@ -6538,11 +6902,15 @@
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Tôi đâu có thực hiện nghi lễ đặc biệt nào, cũng đâu có giữ chiếc chìa khóa nào để dẫn tới nơi này đâu.</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>そこに特別な儀式とかを行ったり、[・|こ][・|こ]へと通ずるための鍵だとかを持っていたわけではない。</t>
+          <t>Tôi đâu có thực hiện nghi lễ đặc biệt nào, cũng đâu có giữ chiếc chìa khóa nào để dẫn tới nơi này đâu.</t>
         </is>
       </c>
     </row>
@@ -6559,11 +6927,15 @@
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Vậy mà khi mở mắt ra lần nữa, tôi lại đang ở đây. Giữa một "Dạ" lộng lẫy hơn cả thế giới ban ngày.</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>だというのに、次に目覚めたとき、ここにいた。真昼の世界よりもきらびやかな“夜”の中。</t>
+          <t>Vậy mà khi mở mắt ra lần nữa, tôi lại đang ở đây. Giữa một "Dạ" lộng lẫy hơn cả thế giới ban ngày.</t>
         </is>
       </c>
     </row>
@@ -6580,11 +6952,15 @@
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Aa...</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>ああ……。</t>
+          <t>Aa...</t>
         </is>
       </c>
     </row>
@@ -6601,11 +6977,15 @@
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Thì ra là vậy.</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>そうか。</t>
+          <t>Thì ra là vậy.</t>
         </is>
       </c>
     </row>
@@ -6626,11 +7006,15 @@
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Nơi này chính là "Dạ Quốc" trong "lời đồn" sao...</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>ここが“噂”の、“夜の国”か</t>
+          <t>Nơi này chính là "Dạ Quốc" trong "lời đồn" sao...</t>
         </is>
       </c>
     </row>
@@ -6647,11 +7031,15 @@
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Tôi vẫn ngước nhìn bầu trời và lẩm bẩm.</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>空を見上げたままつぶやいた。</t>
+          <t>Tôi vẫn ngước nhìn bầu trời và lẩm bẩm.</t>
         </is>
       </c>
     </row>
@@ -6672,11 +7060,15 @@
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Thật sự là, chỉ cần đi ngủ ở thị trấn này... chỉ cần tiếp cận tháp đồng hồ đó là đã có thể tới đây rồi sao...</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>本当に、この町でただ眠るだけで……[・|あ][・|の][・|時][・|計][・|塔][・|に]、[・|近][・|づ][・|く][・|だ][・|け][・|で]。ここに、やって来れるなんて</t>
+          <t>Thật sự là, chỉ cần đi ngủ ở thị trấn này... chỉ cần tiếp cận tháp đồng hồ đó là đã có thể tới đây rồi sao...</t>
         </is>
       </c>
     </row>
@@ -6693,11 +7085,15 @@
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Những cánh hoa anh đào lả tả rơi. Ghé tai lắng nghe, tiếng còi tàu từ xa xăm đang làm rung động không gian.</t>
+        </is>
+      </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>はらはらと降るさくらの花だ。耳を澄ませば遠い汽笛が空気を震わせている。</t>
+          <t>Những cánh hoa anh đào lả tả rơi. Ghé tai lắng nghe, tiếng còi tàu từ xa xăm đang làm rung động không gian.</t>
         </is>
       </c>
     </row>
@@ -6718,11 +7114,15 @@
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -6739,11 +7139,15 @@
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Tôi nhìn quanh một lượt.</t>
+        </is>
+      </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>辺りを見回す。</t>
+          <t>Tôi nhìn quanh một lượt.</t>
         </is>
       </c>
     </row>
@@ -6760,11 +7164,15 @@
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Chúng tôi hướng về mục tiêu này, và đã tìm đến thị trấn hoa anh đào "Sangencho".</t>
+        </is>
+      </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>俺たちは[・|こ][・|こ]を目指し、この町へ――さくらの杜“参禅町”へとやって来た。</t>
+          <t>Chúng tôi hướng về mục tiêu này, và đã tìm đến thị trấn hoa anh đào "Sangencho".</t>
         </is>
       </c>
     </row>
@@ -6781,11 +7189,15 @@
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Bởi vì có thứ chúng tôi đang tìm kiếm.</t>
+        </is>
+      </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>探しているものがあるからだ。</t>
+          <t>Bởi vì có thứ chúng tôi đang tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -6802,11 +7214,15 @@
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Thế nhưng, chỉ nhìn quanh một cách hời hợt thế này thì chẳng thể thấy bóng dáng thứ cần tìm ở đâu cả.</t>
+        </is>
+      </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>しかしふと辺りを見回す程度では、探し出したいものの姿はどこにもなかった。</t>
+          <t>Thế nhưng, chỉ nhìn quanh một cách hời hợt thế này thì chẳng thể thấy bóng dáng thứ cần tìm ở đâu cả.</t>
         </is>
       </c>
     </row>
@@ -6823,11 +7239,15 @@
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Tôi lại nghe thấy "khúc ca" ấy.</t>
+        </is>
+      </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>また、“歌”が聞こえた。</t>
+          <t>Tôi lại nghe thấy "khúc ca" ấy.</t>
         </is>
       </c>
     </row>
@@ -6844,11 +7264,15 @@
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Như bị thôi thúc bởi giai điệu kì diệu đó, tôi vô thức bước đi.</t>
+        </is>
+      </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>その不思議な旋律に促されるように、ふらふらと歩いた。</t>
+          <t>Như bị thôi thúc bởi giai điệu kì diệu đó, tôi vô thức bước đi.</t>
         </is>
       </c>
     </row>
@@ -6865,11 +7289,15 @@
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Đến khi sực nhận ra, tôi đã đứng ở một nhà ga lớn.</t>
+        </is>
+      </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>気づくと大きな駅にいた。</t>
+          <t>Đến khi sực nhận ra, tôi đã đứng ở một nhà ga lớn.</t>
         </is>
       </c>
     </row>
@@ -6886,11 +7314,15 @@
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Những đoàn tàu hơi nước nối đuôi nhau không ngớt chạy vào ga.</t>
+        </is>
+      </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>絶え間なく滑り込んでくる機関車たち。</t>
+          <t>Những đoàn tàu hơi nước nối đuôi nhau không ngớt chạy vào ga.</t>
         </is>
       </c>
     </row>
@@ -6907,11 +7339,15 @@
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Và vô số những thực thể kì dị đang bước lên hoặc bước xuống tàu.</t>
+        </is>
+      </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>そこに乗り込み、下車してくる様々な何か。</t>
+          <t>Và vô số những thực thể kì dị đang bước lên hoặc bước xuống tàu.</t>
         </is>
       </c>
     </row>
@@ -6928,11 +7364,15 @@
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Trong khuôn viên ga tấp nập người qua lại ấy, những cửa hàng san sát nhau thành hàng.</t>
+        </is>
+      </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>[・|そ][・|れ][・|ら]が行き交う構内には、色々な店が軒を連ねていた。</t>
+          <t>Trong khuôn viên ga tấp nập người qua lại ấy, những cửa hàng san sát nhau thành hàng.</t>
         </is>
       </c>
     </row>
@@ -6949,11 +7389,15 @@
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Trông chẳng khác nào một thành phố lớn sầm uất.</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
-          <t>まるで大きな都市のよう。</t>
+          <t>Trông chẳng khác nào một thành phố lớn sầm uất.</t>
         </is>
       </c>
     </row>
@@ -6970,11 +7414,15 @@
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Tôi ngước lên.</t>
+        </is>
+      </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>見上げる。</t>
+          <t>Tôi ngước lên.</t>
         </is>
       </c>
     </row>
@@ -6991,11 +7439,15 @@
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Phía trước mặt là một tháp đồng hồ vô cùng đồ sộ.</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>その先には大きなおおきな時計塔。</t>
+          <t>Phía trước mặt là một tháp đồng hồ vô cùng đồ sộ.</t>
         </is>
       </c>
     </row>
@@ -7012,11 +7464,15 @@
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Mình phải đến đó. Có ai đó đang gọi mình từ tháp đồng hồ ấy. Tôi thầm nghĩ như vậy một cách kì lạ, rồi bước tiếp.</t>
+        </is>
+      </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>あそこに行かなければならない。誰かがあそこで俺のことを呼んでいる。不思議とそう思え、俺は進んだ。</t>
+          <t>Mình phải đến đó. Có ai đó đang gọi mình từ tháp đồng hồ ấy. Tôi thầm nghĩ như vậy một cách kì lạ, rồi bước tiếp.</t>
         </is>
       </c>
     </row>
@@ -7033,11 +7489,15 @@
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Tôi bước vào một con hẻm nhỏ giống như lối đi phụ.</t>
+        </is>
+      </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>裏路地のような場所に入った。</t>
+          <t>Tôi bước vào một con hẻm nhỏ giống như lối đi phụ.</t>
         </is>
       </c>
     </row>
@@ -7054,11 +7514,15 @@
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Ngay lập tức, xung quanh không còn bóng người.</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>すると途端、人気がなくなる。</t>
+          <t>Ngay lập tức, xung quanh không còn bóng người.</t>
         </is>
       </c>
     </row>
@@ -7079,11 +7543,15 @@
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -7100,11 +7568,15 @@
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Đi tiếp vào đây liệu có thực sự ổn không? Cảm giác sợ hãi bất chợt chạy dọc sống lưng tôi.</t>
+        </is>
+      </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>ここを進んでしまっても本当に大丈夫だろうか。ふとした怖さが背筋をぞくりとさせていた。</t>
+          <t>Đi tiếp vào đây liệu có thực sự ổn không? Cảm giác sợ hãi bất chợt chạy dọc sống lưng tôi.</t>
         </is>
       </c>
     </row>
@@ -7121,11 +7593,15 @@
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Nhưng có vẻ như để đến được tháp đồng hồ phía trước, tôi bắt buộc phải đi qua con hẻm này...</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>だが見上げた先の時計塔へは、この通路を抜けていかなければならないようで……。</t>
+          <t>Nhưng có vẻ như để đến được tháp đồng hồ phía trước, tôi bắt buộc phải đi qua con hẻm này...</t>
         </is>
       </c>
     </row>
@@ -7146,11 +7622,15 @@
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>...Ủa?</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
-          <t>……ん？</t>
+          <t>...Ủa?</t>
         </is>
       </c>
     </row>
@@ -7167,11 +7647,15 @@
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Tôi nghe thấy một giọng nói yếu ớt.</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
-          <t>微かな声を聞いた。</t>
+          <t>Tôi nghe thấy một giọng nói yếu ớt.</t>
         </is>
       </c>
     </row>
@@ -7188,11 +7672,15 @@
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Đi được nửa hành lang, tôi thấy một chiếc cầu thang dẫn lên tầng hai. Ngước nhìn lên, phía trước là một màn đêm sâu thẳm nuốt trọn cả lối đi. Nhưng âm thanh ấy lại đang vọng ra từ phía sau bóng tối đó.</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
-          <t>通路を半分くらい進むと、二階へ続く階段があった。見上げたその先には深い闇がある。階段の続く先を飲み込んでいた。その闇の向こうから聞こえてくる。</t>
+          <t>Đi được nửa hành lang, tôi thấy một chiếc cầu thang dẫn lên tầng hai. Ngước nhìn lên, phía trước là một màn đêm sâu thẳm nuốt trọn cả lối đi. Nhưng âm thanh ấy lại đang vọng ra từ phía sau bóng tối đó.</t>
         </is>
       </c>
     </row>
@@ -7209,11 +7697,15 @@
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Đó là một khúc ca.</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
-          <t>歌だ。</t>
+          <t>Đó là một khúc ca.</t>
         </is>
       </c>
     </row>
@@ -7230,11 +7722,15 @@
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Tôi ghé tai lắng nghe.</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
-          <t>耳を澄ませる。</t>
+          <t>Tôi ghé tai lắng nghe.</t>
         </is>
       </c>
     </row>
@@ -7251,11 +7747,15 @@
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Không sai vào đâu được.</t>
+        </is>
+      </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
-          <t>間違いない。</t>
+          <t>Không sai vào đâu được.</t>
         </is>
       </c>
     </row>
@@ -7272,11 +7772,15 @@
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Một khúc ca đang khẽ vọng lại từ bên kia màn đêm.</t>
+        </is>
+      </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
-          <t>闇の向こうから歌が微かに聞こえてくる。</t>
+          <t>Một khúc ca đang khẽ vọng lại từ bên kia màn đêm.</t>
         </is>
       </c>
     </row>
@@ -7293,11 +7797,15 @@
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>...Đó là một bài hát tôi đã biết.</t>
+        </is>
+      </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
-          <t>……[・|知][・|っ][・|て][・|る][・|歌][・|だ]。</t>
+          <t>...Đó là một bài hát tôi đã biết.</t>
         </is>
       </c>
     </row>
@@ -7314,11 +7822,15 @@
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Hơn nữa, còn là bài hát tôi đã nghe đi nghe lại không biết chán.</t>
+        </is>
+      </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
-          <t>それも、飽くことなく繰り返し聞いた歌だった。</t>
+          <t>Hơn nữa, còn là bài hát tôi đã nghe đi nghe lại không biết chán.</t>
         </is>
       </c>
     </row>
@@ -7335,11 +7847,15 @@
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Như bị dẫn lối bởi tiếng hát ấy, tôi bước chân lên cầu thang.</t>
+        </is>
+      </c>
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
-          <t>その歌声に誘われるようにして、階段を一歩、踏み出した。</t>
+          <t>Như bị dẫn lối bởi tiếng hát ấy, tôi bước chân lên cầu thang.</t>
         </is>
       </c>
     </row>
@@ -7356,11 +7872,15 @@
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Rón rén bước lên, tôi đến được hành lang tầng hai.</t>
+        </is>
+      </c>
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
-          <t>恐る恐る辿り着いた二階の通路。</t>
+          <t>Rón rén bước lên, tôi đến được hành lang tầng hai.</t>
         </is>
       </c>
     </row>
@@ -7377,11 +7897,15 @@
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Tôi dừng chân trước một cánh cửa chạm khắc hoa văn cổ kính.</t>
+        </is>
+      </c>
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
-          <t>アンティーク調の彫刻が刻まれた扉の前に行き着く。</t>
+          <t>Tôi dừng chân trước một cánh cửa chạm khắc hoa văn cổ kính.</t>
         </is>
       </c>
     </row>
@@ -7398,11 +7922,15 @@
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Có vẻ như tiếng hát đang vang lên từ phía sau cánh cửa đó.</t>
+        </is>
+      </c>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
-          <t>歌はその向こうから聞こえてきているようだった。</t>
+          <t>Có vẻ như tiếng hát đang vang lên từ phía sau cánh cửa đó.</t>
         </is>
       </c>
     </row>
@@ -7419,11 +7947,15 @@
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Âm sắc ấy gợi cảm giác như âm thanh đĩa than phát ra từ chiếc máy hát cổ.</t>
+        </is>
+      </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr">
         <is>
-          <t>古い蓄音機から響いてくるレコードの音。そんな印象の音色だった。</t>
+          <t>Âm sắc ấy gợi cảm giác như âm thanh đĩa than phát ra từ chiếc máy hát cổ.</t>
         </is>
       </c>
     </row>
@@ -7440,11 +7972,15 @@
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Tôi nắm lấy nắm cửa.</t>
+        </is>
+      </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
-          <t>ドアノブを握る。</t>
+          <t>Tôi nắm lấy nắm cửa.</t>
         </is>
       </c>
     </row>
@@ -7465,11 +8001,15 @@
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -7486,11 +8026,15 @@
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Vặn nó lúc này liệu có sao không?</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>これを回してしまって平気だろうか。</t>
+          <t>Vặn nó lúc này liệu có sao không?</t>
         </is>
       </c>
     </row>
@@ -7507,11 +8051,15 @@
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Thứ đang chờ đợi tôi phía trước có thể là một cơn ác mộng, hoặc cũng có thể là một vở hài kịch vui vẻ khiến người ta chỉ muốn mãi đắm chìm mà không bao giờ muốn tỉnh giấc.</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
-          <t>[・|こ][・|れ]より先に待っているのは悪夢かもしれないし、いつまでも目覚めることなく続いてほしいと祈れるほどの、楽しいばかりの喜劇かもしれない。</t>
+          <t>Thứ đang chờ đợi tôi phía trước có thể là một cơn ác mộng, hoặc cũng có thể là một vở hài kịch vui vẻ khiến người ta chỉ muốn mãi đắm chìm mà không bao giờ muốn tỉnh giấc.</t>
         </is>
       </c>
     </row>
@@ -7528,11 +8076,15 @@
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Thứ mà tôi đã tìm kiếm suốt bấy lâu nay đang ở ngay sau đây.</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
-          <t>長い、ながい間、探し続けたものがこの先にある。</t>
+          <t>Thứ mà tôi đã tìm kiếm suốt bấy lâu nay đang ở ngay sau đây.</t>
         </is>
       </c>
     </row>
@@ -7549,11 +8101,15 @@
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Niềm kì vọng ấy cũng song hành trong lòng tôi...</t>
+        </is>
+      </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
-          <t>そんな期待も同時にあって……。</t>
+          <t>Niềm kì vọng ấy cũng song hành trong lòng tôi...</t>
         </is>
       </c>
     </row>
@@ -7570,11 +8126,15 @@
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Tôi ngập ngừng.</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
-          <t>逡巡する。</t>
+          <t>Tôi ngập ngừng.</t>
         </is>
       </c>
     </row>
@@ -7591,11 +8151,15 @@
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Cũng có một chút sợ hãi.</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
-          <t>若干の怖さもあった。</t>
+          <t>Cũng có một chút sợ hãi.</t>
         </is>
       </c>
     </row>
@@ -7612,11 +8176,15 @@
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Thế nhưng, quay lưng bỏ chạy lúc này— tuyệt đối không phải là lựa chọn của tôi.</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr">
         <is>
-          <t>しかしこのまま背を向け、引き返す――そんな選択だけはなかった。</t>
+          <t>Thế nhưng, quay lưng bỏ chạy lúc này— tuyệt đối không phải là lựa chọn của tôi.</t>
         </is>
       </c>
     </row>
@@ -7633,11 +8201,15 @@
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Tôi chậm rãi vặn nắm cửa.</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>ゆっくりとノブを回し。</t>
+          <t>Tôi chậm rãi vặn nắm cửa.</t>
         </is>
       </c>
     </row>
@@ -7654,11 +8226,15 @@
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Cẩn thận đẩy cánh cửa ra...</t>
+        </is>
+      </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>慎重に、扉を押して……。</t>
+          <t>Cẩn thận đẩy cánh cửa ra...</t>
         </is>
       </c>
     </row>
@@ -7675,11 +8251,15 @@
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Tôi mở cửa.</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
-          <t>開く。</t>
+          <t>Tôi mở cửa.</t>
         </is>
       </c>
     </row>
@@ -7696,11 +8276,15 @@
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>...Khúc hát bỗng vang lên to hơn.</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
-          <t>……歌が、大きくなった。</t>
+          <t>...Khúc hát bỗng vang lên to hơn.</t>
         </is>
       </c>
     </row>
@@ -7717,11 +8301,15 @@
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Ngay khi cánh cửa mở ra, giai điệu vốn đong đầy trong phòng bỗng chốc tràn ra ngoài.</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr">
         <is>
-          <t>扉を開いた瞬間に、室内を満たしていたのだろう旋律が、一気にこぼれ出してきたのだ。</t>
+          <t>Ngay khi cánh cửa mở ra, giai điệu vốn đong đầy trong phòng bỗng chốc tràn ra ngoài.</t>
         </is>
       </c>
     </row>
@@ -7738,11 +8326,15 @@
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Nơi đó là phòng điều khiển của tháp đồng hồ.</t>
+        </is>
+      </c>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr">
         <is>
-          <t>そこは時計塔の管理室だった。</t>
+          <t>Nơi đó là phòng điều khiển của tháp đồng hồ.</t>
         </is>
       </c>
     </row>
@@ -7759,11 +8351,15 @@
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Không chỉ có tiếng hát.</t>
+        </is>
+      </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
-          <t>歌だけではない。</t>
+          <t>Không chỉ có tiếng hát.</t>
         </is>
       </c>
     </row>
@@ -7780,11 +8376,15 @@
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Có cả những âm thanh kèn kẹt nặng nề, khô khốc vang lên.</t>
+        </is>
+      </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
-          <t>ぎりぎりと、重く苦しい音がしている。</t>
+          <t>Có cả những âm thanh kèn kẹt nặng nề, khô khốc vang lên.</t>
         </is>
       </c>
     </row>
@@ -7801,11 +8401,15 @@
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Đó là tiếng những bánh răng đang quay để liên tục dịch chuyển kim giây của chiếc đồng hồ khổng lồ.</t>
+        </is>
+      </c>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
-          <t>それは巨大な時計の秒針を、絶え間なく進めるために回転する歯車の音。</t>
+          <t>Đó là tiếng những bánh răng đang quay để liên tục dịch chuyển kim giây của chiếc đồng hồ khổng lồ.</t>
         </is>
       </c>
     </row>
@@ -7822,11 +8426,15 @@
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Bên trong mặt số đồng hồ. Trên những bức tường của căn phòng, các bánh răng trần vẫn không ngừng chuyển động.</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
-          <t>時計盤の裏側だ。部屋の壁面には、むき出しの歯車などが回転し続けている。</t>
+          <t>Bên trong mặt số đồng hồ. Trên những bức tường của căn phòng, các bánh răng trần vẫn không ngừng chuyển động.</t>
         </is>
       </c>
     </row>
@@ -7843,11 +8451,15 @@
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Một chiếc máy hát cổ được đặt ngay chính giữa căn phòng đó.</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
-          <t>そんな部屋の中心に蓄音機は置かれていた。</t>
+          <t>Một chiếc máy hát cổ được đặt ngay chính giữa căn phòng đó.</t>
         </is>
       </c>
     </row>
@@ -7864,11 +8476,15 @@
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Tiếng hát phát ra từ đó, vang vọng khắp "Dạ".</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
-          <t>そこから歌が鳴り、“夜”に響いている。</t>
+          <t>Tiếng hát phát ra từ đó, vang vọng khắp "Dạ".</t>
         </is>
       </c>
     </row>
@@ -7885,11 +8501,15 @@
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Trong căn phòng không mấy rộng rãi ấy, ngoài những đĩa hát ra còn chất đầy sách vở và tranh ảnh.</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
-          <t>広くもないその部屋には、レコードだけではなく、たくさんの本や絵などが置かれていた。</t>
+          <t>Trong căn phòng không mấy rộng rãi ấy, ngoài những đĩa hát ra còn chất đầy sách vở và tranh ảnh.</t>
         </is>
       </c>
     </row>
@@ -7910,11 +8530,15 @@
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -7931,11 +8555,15 @@
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Cuối cùng, tôi cũng tìm thấy.</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
-          <t>[・|や][・|っ][・|と]、[・|見][・|つ][・|け][・|た]。</t>
+          <t>Cuối cùng, tôi cũng tìm thấy.</t>
         </is>
       </c>
     </row>
@@ -7952,11 +8580,15 @@
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Có một cô gái đang ở đó.</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
-          <t>女の子がいた。</t>
+          <t>Có một cô gái đang ở đó.</t>
         </is>
       </c>
     </row>
@@ -7973,11 +8605,15 @@
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Một mái tóc dài thướt tha cùng bộ váy lộng lẫy. Làn da trắng ngần như ngọc.</t>
+        </is>
+      </c>
       <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
-          <t>きらびやかなドレスに長い髪。透き通るような白い肌。</t>
+          <t>Một mái tóc dài thướt tha cùng bộ váy lộng lẫy. Làn da trắng ngần như ngọc.</t>
         </is>
       </c>
     </row>
@@ -7994,11 +8630,15 @@
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Cô ấy khẽ nhắm mắt, lặng im lắng nghe khúc ca đang vang lên từ máy hát.</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
-          <t>そっと[まぶた|瞼]を閉じ、そこから響く歌に耳を澄ませていた。</t>
+          <t>Cô ấy khẽ nhắm mắt, lặng im lắng nghe khúc ca đang vang lên từ máy hát.</t>
         </is>
       </c>
     </row>
@@ -8015,11 +8655,15 @@
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Dáng vẻ đó trông giống hệt như...</t>
+        </is>
+      </c>
       <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
-          <t>その姿はまるで……。</t>
+          <t>Dáng vẻ đó trông giống hệt như...</t>
         </is>
       </c>
     </row>
@@ -8040,11 +8684,15 @@
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>...Trông giống như một chú cún con vậy.</t>
+        </is>
+      </c>
       <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
-          <t>……[・|ま][・|る][・|で]、[・|子][・|犬][・|み][・|た][・|い][・|だ]</t>
+          <t>...Trông giống như một chú cún con vậy.</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8709,15 @@
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>...Những lời nói đó vô thức bật ra khỏi miệng tôi.</t>
+        </is>
+      </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
-          <t>……そんな言葉が、思わず口からこぼれてしまっていた。</t>
+          <t>...Những lời nói đó vô thức bật ra khỏi miệng tôi.</t>
         </is>
       </c>
     </row>
@@ -8086,11 +8738,15 @@
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>...Hả?</t>
+        </is>
+      </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
-          <t>……え？</t>
+          <t>...Hả?</t>
         </is>
       </c>
     </row>
@@ -8107,11 +8763,15 @@
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Cô gái mở mắt ra.</t>
+        </is>
+      </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
-          <t>女の子が[まぶた|瞼]を開く。</t>
+          <t>Cô gái mở mắt ra.</t>
         </is>
       </c>
     </row>
@@ -8128,11 +8788,15 @@
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Cô ấy quay đầu lại nhìn tôi với gương mặt ngơ ngác đầy ngạc nhiên.</t>
+        </is>
+      </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
-          <t>そしてこちらを振り向いた。驚いた顔だった。</t>
+          <t>Cô ấy quay đầu lại nhìn tôi với gương mặt ngơ ngác đầy ngạc nhiên.</t>
         </is>
       </c>
     </row>
@@ -8153,11 +8817,15 @@
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>...Cún con?</t>
+        </is>
+      </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
-          <t>……子犬？</t>
+          <t>...Cún con?</t>
         </is>
       </c>
     </row>
@@ -8174,11 +8842,15 @@
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Hóa ra điều đầu tiên cô ấy bận tâm lại là cái đó sao. Thay vì ngạc nhiên hay chất vấn sự xuất hiện của kẻ đột nhập là tôi.</t>
+        </is>
+      </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
-          <t>まず気にするところはそこなのか。侵入者の存在に驚くでも糾弾するでもなく。</t>
+          <t>Hóa ra điều đầu tiên cô ấy bận tâm lại là cái đó sao. Thay vì ngạc nhiên hay chất vấn sự xuất hiện của kẻ đột nhập là tôi.</t>
         </is>
       </c>
     </row>
@@ -8195,11 +8867,15 @@
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Không hiểu sao khoé miệng tôi lại khẽ nhếch lên mỉm cười và nói— dẫu chính bản thân tôi cũng tự hỏi liệu đây có phải là chuyện nên nói vào lúc này hay không.</t>
+        </is>
+      </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
-          <t>どうしてだか口元を緩ませながら、俺は言う――[・|俺][・|自][・|身][・|も][・|ま][・|た]、[・|今][・|話][・|す][・|べ][・|き][・|は][・|そ][・|う][・|い][・|う][・|こ][・|と][・|な][・|の][・|か][・|な][・|と][・|思][・|い][・|な][・|が][・|ら][・|も]。</t>
+          <t>Không hiểu sao khoé miệng tôi lại khẽ nhếch lên mỉm cười và nói— dẫu chính bản thân tôi cũng tự hỏi liệu đây có phải là chuyện nên nói vào lúc này hay không.</t>
         </is>
       </c>
     </row>
@@ -8220,11 +8896,15 @@
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Có một hãng sản xuất loa và thiết bị âm thanh ấy.</t>
+        </is>
+      </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
-          <t>スピーカーとかのメーカーでさ</t>
+          <t>Có một hãng sản xuất loa và thiết bị âm thanh ấy.</t>
         </is>
       </c>
     </row>
@@ -8245,11 +8925,15 @@
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>...Hãng sản xuất sao?</t>
+        </is>
+      </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
-          <t>……メーカー？</t>
+          <t>...Hãng sản xuất sao?</t>
         </is>
       </c>
     </row>
@@ -8270,11 +8954,15 @@
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>...Ừm.</t>
+        </is>
+      </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
-          <t>……うん</t>
+          <t>...Ừm.</t>
         </is>
       </c>
     </row>
@@ -8295,11 +8983,15 @@
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Thì cái đó đó. Có một logo rất nổi tiếng vẽ hình chú cún con ngồi trước một chiếc máy hát cổ và khẽ nghiêng đầu ấy.</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
-          <t>ほら、あれだよ。子犬が蓄音機の前に座って、首をかしげてる――そんな有名なロゴマークがあるよね</t>
+          <t>Thì cái đó đó. Có một logo rất nổi tiếng vẽ hình chú cún con ngồi trước một chiếc máy hát cổ và khẽ nghiêng đầu ấy.</t>
         </is>
       </c>
     </row>
@@ -8320,11 +9012,15 @@
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Ừm. Đúng thế thật.</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
-          <t>うん。そうだね</t>
+          <t>Ừm. Đúng thế thật.</t>
         </is>
       </c>
     </row>
@@ -8341,11 +9037,15 @@
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>"Tớ từng thấy rồi." Cô gái gật đầu.</t>
+        </is>
+      </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
-          <t>見たことあるよと、女の子はうなずく。</t>
+          <t>"Tớ từng thấy rồi." Cô gái gật đầu.</t>
         </is>
       </c>
     </row>
@@ -8366,11 +9066,15 @@
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Từ chiếc máy hát đó phát ra giọng nói của người chủ đã khuất của chú cún... Chú cún cứ ngồi đó mãi không rời, nghển cổ nhìn vào chiếc máy đang phát ra giọng nói của người chủ mà nó yêu quý nhất—</t>
+        </is>
+      </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
-          <t>あの蓄音機からは、亡くなった子犬の飼い主の声が流れていて……。子犬はずっとああして、蓄音機の前から離れず、大好きだった主人の声がする機械を覗き込んでいる――</t>
+          <t>Từ chiếc máy hát đó phát ra giọng nói của người chủ đã khuất của chú cún... Chú cún cứ ngồi đó mãi không rời, nghển cổ nhìn vào chiếc máy đang phát ra giọng nói của người chủ mà nó yêu quý nhất—</t>
         </is>
       </c>
     </row>
@@ -8387,11 +9091,15 @@
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Bức ảnh chụp lại khoảnh khắc tưởng nhớ chú cún ấy đã trở thành biểu tượng của công ty.</t>
+        </is>
+      </c>
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
-          <t>そんな子犬の姿を[しの|偲]び、撮られた写真が、会社のシンボルとなった。</t>
+          <t>Bức ảnh chụp lại khoảnh khắc tưởng nhớ chú cún ấy đã trở thành biểu tượng của công ty.</t>
         </is>
       </c>
     </row>
@@ -8408,11 +9116,15 @@
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Có một giai thoại, hay nói đúng hơn là một "tin đồn" như vậy đấy...</t>
+        </is>
+      </c>
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
-          <t>そんな逸話というか、“噂話”があるけれど……。</t>
+          <t>Có một giai thoại, hay nói đúng hơn là một "tin đồn" như vậy đấy...</t>
         </is>
       </c>
     </row>
@@ -8433,11 +9145,15 @@
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Chỉ là tớ cảm giác cậu trông rất giống chú cún con đó...</t>
+        </is>
+      </c>
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
-          <t>なんだか君が、その子犬みたいに見えたから……</t>
+          <t>Chỉ là tớ cảm giác cậu trông rất giống chú cún con đó...</t>
         </is>
       </c>
     </row>
@@ -8458,11 +9174,15 @@
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
-          <t>…………</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8479,11 +9199,15 @@
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Cô gái chớp chớp đôi mắt to tròn.</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
-          <t>女の子は大きな目をぱちぱちとさせる。</t>
+          <t>Cô gái chớp chớp đôi mắt to tròn.</t>
         </is>
       </c>
     </row>
@@ -8504,11 +9228,15 @@
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Chú cún con đó... liệu có gặp lại được người chủ yêu quý của mình không?</t>
+        </is>
+      </c>
       <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
-          <t>その子犬は、大切なご主人に会えたのかな</t>
+          <t>Chú cún con đó... liệu có gặp lại được người chủ yêu quý của mình không?</t>
         </is>
       </c>
     </row>
@@ -8529,11 +9257,15 @@
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>...Đời nào chứ.</t>
+        </is>
+      </c>
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
-          <t>……まさか</t>
+          <t>...Đời nào chứ.</t>
         </is>
       </c>
     </row>
@@ -8550,11 +9282,15 @@
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Tôi lắc đầu.</t>
+        </is>
+      </c>
       <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
-          <t>首を振る。</t>
+          <t>Tôi lắc đầu.</t>
         </is>
       </c>
     </row>
@@ -8575,11 +9311,15 @@
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>...Kẻ còn sống không bao giờ có thể gặp lại người đã khuất. Thế nên—</t>
+        </is>
+      </c>
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
-          <t>……命あるものは、死んでしまったものとは二度と会えない。だから――</t>
+          <t>...Kẻ còn sống không bao giờ có thể gặp lại người đã khuất. Thế nên—</t>
         </is>
       </c>
     </row>
@@ -8596,11 +9336,15 @@
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>—Chắc chắn hai người họ đã không thể gặp lại nhau.</t>
+        </is>
+      </c>
       <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
-          <t>――きっと[・|ふ][・|た][・|り]は出会えなかった。</t>
+          <t>—Chắc chắn hai người họ đã không thể gặp lại nhau.</t>
         </is>
       </c>
     </row>
@@ -8621,11 +9365,15 @@
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Đúng vậy nhỉ...</t>
+        </is>
+      </c>
       <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
-          <t>そうだね……</t>
+          <t>Đúng vậy nhỉ...</t>
         </is>
       </c>
     </row>
@@ -8642,11 +9390,15 @@
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Thay vì gật đầu, cô gái khẽ nghiêng đầu.</t>
+        </is>
+      </c>
       <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
-          <t>うなずく代わりに、女の子は小首をかしげた。</t>
+          <t>Thay vì gật đầu, cô gái khẽ nghiêng đầu.</t>
         </is>
       </c>
     </row>
@@ -8663,11 +9415,15 @@
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>...Giống hệt chú cún con kia.</t>
+        </is>
+      </c>
       <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
-          <t>……[・|あ][・|の]子犬のように。</t>
+          <t>...Giống hệt chú cún con kia.</t>
         </is>
       </c>
     </row>
@@ -8684,11 +9440,15 @@
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Có điều, hành động ấy không hướng về chiếc máy hát trước mặt, mà là hướng về kẻ vừa đột ngột xuất hiện như tôi.</t>
+        </is>
+      </c>
       <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
-          <t>だけどそれは、目の前の蓄音機に向かってではなく、突然現れた俺に向かってだ。</t>
+          <t>Có điều, hành động ấy không hướng về chiếc máy hát trước mặt, mà là hướng về kẻ vừa đột ngột xuất hiện như tôi.</t>
         </is>
       </c>
     </row>
@@ -8709,11 +9469,15 @@
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Cậu là...</t>
+        </is>
+      </c>
       <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
-          <t>あなたは……</t>
+          <t>Cậu là...</t>
         </is>
       </c>
     </row>
@@ -8730,11 +9494,15 @@
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>"Ai vậy?"</t>
+        </is>
+      </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
-          <t>“誰？”</t>
+          <t>"Ai vậy?"</t>
         </is>
       </c>
     </row>
@@ -8751,11 +9519,15 @@
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Tôi cứ ngỡ cô ấy sẽ hỏi như vậy, thế nhưng—</t>
+        </is>
+      </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
-          <t>そう問われるのかと、思ったけれど、</t>
+          <t>Tôi cứ ngỡ cô ấy sẽ hỏi như vậy, thế nhưng—</t>
         </is>
       </c>
     </row>
@@ -8776,11 +9548,15 @@
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Taiga.</t>
+        </is>
+      </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
-          <t>大雅</t>
+          <t>Taiga.</t>
         </is>
       </c>
     </row>
@@ -8801,11 +9577,15 @@
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Hả?</t>
+        </is>
+      </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr">
         <is>
-          <t>え？</t>
+          <t>Hả?</t>
         </is>
       </c>
     </row>
@@ -8826,11 +9606,15 @@
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
-      <c r="E354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Kanade, Taiga...</t>
+        </is>
+      </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
-          <t>奏、大雅……</t>
+          <t>Kanade, Taiga...</t>
         </is>
       </c>
     </row>
@@ -8847,11 +9631,15 @@
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>"Đúng vậy không?" Cô gái mỉm cười nhẹ nhàng và nghiêng đầu hỏi.</t>
+        </is>
+      </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
-          <t>そうだよね？　と淡い微笑みと共に、女の子は首をかしげた。</t>
+          <t>"Đúng vậy không?" Cô gái mỉm cười nhẹ nhàng và nghiêng đầu hỏi.</t>
         </is>
       </c>
     </row>
@@ -8872,11 +9660,15 @@
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Sao cậu lại biết tên tớ?</t>
+        </is>
+      </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
-          <t>どうして、俺の名前を</t>
+          <t>Sao cậu lại biết tên tớ?</t>
         </is>
       </c>
     </row>
@@ -8897,11 +9689,15 @@
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Tớ biết chứ.</t>
+        </is>
+      </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
-          <t>知ってるよ</t>
+          <t>Tớ biết chứ.</t>
         </is>
       </c>
     </row>
@@ -8918,11 +9714,15 @@
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Ngay lúc ấy, khúc ca phát ra từ máy hát cũng vừa kết thúc.</t>
+        </is>
+      </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
-          <t>そこで、蓄音機から流れていた歌が終わった。</t>
+          <t>Ngay lúc ấy, khúc ca phát ra từ máy hát cũng vừa kết thúc.</t>
         </is>
       </c>
     </row>
@@ -8943,11 +9743,15 @@
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Chú cún tin tưởng đợi chủ nhân trở về có lẽ đã mãi mãi không thể gặp lại người nó yêu quý... Nhưng tớ thì khác, tớ đã gặp được cậu rồi này—</t>
+        </is>
+      </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr">
         <is>
-          <t>飼い主の帰りを信じて待っていた子犬は、大切な人と、もう二度と会えなかったかもしれないけれど……でもね。私は、あなたと会えたよ――</t>
+          <t>Chú cún tin tưởng đợi chủ nhân trở về có lẽ đã mãi mãi không thể gặp lại người nó yêu quý... Nhưng tớ thì khác, tớ đã gặp được cậu rồi này—</t>
         </is>
       </c>
     </row>
@@ -8964,11 +9768,15 @@
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Cô gái nói.</t>
+        </is>
+      </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
-          <t>女の子は、言う。</t>
+          <t>Cô gái nói.</t>
         </is>
       </c>
     </row>
@@ -8989,11 +9797,15 @@
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Khoảnh khắc được gặp cậu trong "Dạ" thế này, tớ đã luôn chờ đợi từ rất lâu về trước—</t>
+        </is>
+      </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
-          <t>私は、あなたとこうして会える“夜”のことを、ずっと、昔から――</t>
+          <t>Khoảnh khắc được gặp cậu trong "Dạ" thế này, tớ đã luôn chờ đợi từ rất lâu về trước—</t>
         </is>
       </c>
     </row>
@@ -9014,11 +9826,15 @@
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Tớ đã chờ đợi cậu từ rất lâu, rất lâu trước cả khi cậu được sinh ra trên thế giới này đấy.</t>
+        </is>
+      </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
-          <t>あなたがこの世界に生まれてくるずっとずっと前から、待っていたんだよ</t>
+          <t>Tớ đã chờ đợi cậu từ rất lâu, rất lâu trước cả khi cậu được sinh ra trên thế giới này đấy.</t>
         </is>
       </c>
     </row>
